--- a/projeto hotel/db/clientes.xlsx
+++ b/projeto hotel/db/clientes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,10 +487,80 @@
           <t>Rua dos Bobos</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>lerolero</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>74185263</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>kljwfn@llsjdnfk</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>123456789</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>asdfghjkl</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Emanuelly de Lara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>4141414141</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>email.email@email.com</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>40028922</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Avenida Getúlio Vargas, 422</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
         </is>
       </c>
     </row>

--- a/projeto hotel/db/clientes.xlsx
+++ b/projeto hotel/db/clientes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -557,10 +557,45 @@
           <t>Avenida Getúlio Vargas, 422</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>2026-05-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>thais</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>86577622</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>luiz.oliveira.matos@escola.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>418998873</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>rua mandirituba</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
